--- a/artfynd/A 42616-2024 artfynd.xlsx
+++ b/artfynd/A 42616-2024 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>121067915</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
